--- a/src/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/LPC/compressor_stage_2_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.0016587594588024957</v>
       </c>
       <c r="B2">
-        <v>0.0019821145684673484</v>
+        <v>0.0017366181685645793</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0033175189176049913</v>
       </c>
       <c r="B3">
-        <v>0.0031552085197309888</v>
+        <v>0.0028168215901352802</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.0049762783764074874</v>
       </c>
       <c r="B4">
-        <v>0.00417749275068416</v>
+        <v>0.003767447412468183</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0066350378352099827</v>
       </c>
       <c r="B5">
-        <v>0.00508667054311105</v>
+        <v>0.0046189003757287454</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0082937972940124779</v>
       </c>
       <c r="B6">
-        <v>0.0058987069692878688</v>
+        <v>0.005384172121179291</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0099525567528149748</v>
       </c>
       <c r="B7">
-        <v>0.0066230482924864416</v>
+        <v>0.0060710131445969708</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.01161131621161747</v>
       </c>
       <c r="B8">
-        <v>0.0072655803489272575</v>
+        <v>0.0066843136212748622</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.013270075670419965</v>
       </c>
       <c r="B9">
-        <v>0.00783488090193078</v>
+        <v>0.0072310924589266716</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.014928835129222461</v>
       </c>
       <c r="B10">
-        <v>0.0083400946136565311</v>
+        <v>0.0077188108747453955</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.016587594588024956</v>
       </c>
       <c r="B11">
-        <v>0.0087899418145202975</v>
+        <v>0.00815457059142059</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.018246354046827454</v>
       </c>
       <c r="B12">
-        <v>0.00918931761145281</v>
+        <v>0.00854240378267989</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.01990511350562995</v>
       </c>
       <c r="B13">
-        <v>0.0095282405491883184</v>
+        <v>0.0088744239209067252</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B14">
-        <v>0.0098008928279690391</v>
+        <v>0.0091460668869886089</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.02322263242323494</v>
       </c>
       <c r="B15">
-        <v>0.010032987832265538</v>
+        <v>0.0093779768971736076</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.024881391882037432</v>
       </c>
       <c r="B16">
-        <v>0.010248105851282203</v>
+        <v>0.0095890848234503837</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.026540151340839931</v>
       </c>
       <c r="B17">
-        <v>0.010429763608930357</v>
+        <v>0.00976625982540936</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.028198910799642429</v>
       </c>
       <c r="B18">
-        <v>0.01055655614967546</v>
+        <v>0.00989242552113202</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.029857670258444921</v>
       </c>
       <c r="B19">
-        <v>0.010627455365492599</v>
+        <v>0.009966785075062299</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.03151642971724742</v>
       </c>
       <c r="B20">
-        <v>0.010646527360234267</v>
+        <v>0.009992611538234759</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.033175189176049912</v>
       </c>
       <c r="B21">
-        <v>0.010617838237752957</v>
+        <v>0.0099731779616839544</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.03483394863485241</v>
       </c>
       <c r="B22">
-        <v>0.010544715599480505</v>
+        <v>0.0099111600129679778</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.036492708093654909</v>
       </c>
       <c r="B23">
-        <v>0.010427533037166106</v>
+        <v>0.00980684382573907</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.0381514675524574</v>
       </c>
       <c r="B24">
-        <v>0.010265925640138306</v>
+        <v>0.0096599181501730146</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.0398102270112599</v>
       </c>
       <c r="B25">
-        <v>0.01005952849772564</v>
+        <v>0.0094700717364455851</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.041468986470062391</v>
       </c>
       <c r="B26">
-        <v>0.00980782744863233</v>
+        <v>0.00923686726527617</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B27">
-        <v>0.0095097113290652773</v>
+        <v>0.0089593631395585571</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.044786505387667382</v>
       </c>
       <c r="B28">
-        <v>0.0091639197246070718</v>
+        <v>0.0086364916927301368</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.04644526484646988</v>
       </c>
       <c r="B29">
-        <v>0.0087691922208402943</v>
+        <v>0.0082671852582283066</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.048104024305272379</v>
       </c>
       <c r="B30">
-        <v>0.00832475605249762</v>
+        <v>0.0078507585288826974</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.049762783764074864</v>
       </c>
       <c r="B31">
-        <v>0.0078317890509121014</v>
+        <v>0.0073880556350919063</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.051421543222877363</v>
       </c>
       <c r="B32">
-        <v>0.0072919566965668741</v>
+        <v>0.006880303066646767</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.053080302681679861</v>
       </c>
       <c r="B33">
-        <v>0.0067069244699450824</v>
+        <v>0.0063287273133381134</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.05473906214048236</v>
       </c>
       <c r="B34">
-        <v>0.0060774557698277986</v>
+        <v>0.0057338226816926107</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.056397821599284859</v>
       </c>
       <c r="B35">
-        <v>0.005400705668187818</v>
+        <v>0.0050931547451802317</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.058056581058087343</v>
       </c>
       <c r="B36">
-        <v>0.0046729271552958746</v>
+        <v>0.0044035568940067821</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.059715340516889842</v>
       </c>
       <c r="B37">
-        <v>0.0038903732214226896</v>
+        <v>0.0036618625183780576</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.061374099975692341</v>
       </c>
       <c r="B38">
-        <v>0.0030471489961900549</v>
+        <v>0.0028631739526338235</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.06303285943449484</v>
       </c>
       <c r="B39">
-        <v>0.0021287681666240007</v>
+        <v>0.0019956693076496885</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B40">
-        <v>0.0011185965591016169</v>
+        <v>0.0010457956384352224</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -669,7 +669,7 @@
         <v>0.066350378352099823</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>-2.301991179346618E-19</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B43">
-        <v>0.00039058735243767092</v>
+        <v>0.00046338827310406569</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.06303285943449484</v>
       </c>
       <c r="B44">
-        <v>0.0007977795768808805</v>
+        <v>0.00093087843585519254</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.061374099975692341</v>
       </c>
       <c r="B45">
-        <v>0.0012073985606277423</v>
+        <v>0.0013913736041839737</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.059715340516889842</v>
       </c>
       <c r="B46">
-        <v>0.0016052661909763716</v>
+        <v>0.0018337768940210034</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.058056581058087343</v>
       </c>
       <c r="B47">
-        <v>0.0019792245424049542</v>
+        <v>0.0022485948036940462</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.056397821599284859</v>
       </c>
       <c r="B48">
-        <v>0.0023251964381119576</v>
+        <v>0.0026327473611195439</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.05473906214048236</v>
       </c>
       <c r="B49">
-        <v>0.0026411248884759247</v>
+        <v>0.0029847579766111121</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.053080302681679861</v>
       </c>
       <c r="B50">
-        <v>0.0029249529038753923</v>
+        <v>0.0033031500604823617</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.051421543222877363</v>
       </c>
       <c r="B51">
-        <v>0.0031754203973657965</v>
+        <v>0.0035870740272859049</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.049762783764074864</v>
       </c>
       <c r="B52">
-        <v>0.0033944548927101587</v>
+        <v>0.0038381883085303529</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.048104024305272379</v>
       </c>
       <c r="B53">
-        <v>0.0035847808163483939</v>
+        <v>0.0040587783399633169</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.04644526484646988</v>
       </c>
       <c r="B54">
-        <v>0.0037491225947204219</v>
+        <v>0.0042511295573324087</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.044786505387667382</v>
       </c>
       <c r="B55">
-        <v>0.0038896394058377248</v>
+        <v>0.00441706743771466</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B56">
-        <v>0.0040062294339980572</v>
+        <v>0.0045565776235047791</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.041468986470062391</v>
       </c>
       <c r="B57">
-        <v>0.00409822561507074</v>
+        <v>0.0046691857984268986</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.0398102270112599</v>
       </c>
       <c r="B58">
-        <v>0.0041649608849250929</v>
+        <v>0.0047544176462051479</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.0381514675524574</v>
       </c>
       <c r="B59">
-        <v>0.0042058507404853949</v>
+        <v>0.0048118582304506868</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.036492708093654909</v>
       </c>
       <c r="B60">
-        <v>0.0042206409228957575</v>
+        <v>0.0048413301343227929</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.03483394863485241</v>
       </c>
       <c r="B61">
-        <v>0.00420915973435525</v>
+        <v>0.0048427153208677751</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.033175189176049912</v>
       </c>
       <c r="B62">
-        <v>0.0041712354770629375</v>
+        <v>0.0048158957531319393</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.03151642971724742</v>
       </c>
       <c r="B63">
-        <v>0.0041073691402391931</v>
+        <v>0.0047612849622387012</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.029857670258444921</v>
       </c>
       <c r="B64">
-        <v>0.0040207524611895968</v>
+        <v>0.0046814227516198967</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.028198910799642429</v>
       </c>
       <c r="B65">
-        <v>0.00391524986424103</v>
+        <v>0.004579380492784473</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.026540151340839931</v>
       </c>
       <c r="B66">
-        <v>0.0037947257737203756</v>
+        <v>0.004458229557241373</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.024881391882037432</v>
       </c>
       <c r="B67">
-        <v>0.0036578955729640039</v>
+        <v>0.0043169166007958233</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.02322263242323494</v>
       </c>
       <c r="B68">
-        <v>0.0034828784813462433</v>
+        <v>0.0041378894164381726</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B69">
-        <v>0.0032526334181647311</v>
+        <v>0.0039074593591451618</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.01990511350562995</v>
       </c>
       <c r="B70">
-        <v>0.0029900742663724008</v>
+        <v>0.0036438908946539927</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.018246354046827454</v>
       </c>
       <c r="B71">
-        <v>0.0027201793237236218</v>
+        <v>0.0033670931524965408</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.016587594588024956</v>
       </c>
       <c r="B72">
-        <v>0.0024362295835232174</v>
+        <v>0.0030716008066229254</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.014928835129222461</v>
       </c>
       <c r="B73">
-        <v>0.0021272572245451772</v>
+        <v>0.0027485409634563128</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.013270075670419965</v>
       </c>
       <c r="B74">
-        <v>0.0017969964718896952</v>
+        <v>0.0024007849148938039</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.01161131621161747</v>
       </c>
       <c r="B75">
-        <v>0.0014529130724033111</v>
+        <v>0.0020341798000557058</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0099525567528149748</v>
       </c>
       <c r="B76">
-        <v>0.0011026968135917359</v>
+        <v>0.0016547319614812065</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0082937972940124779</v>
       </c>
       <c r="B77">
-        <v>0.000753358488202096</v>
+        <v>0.0012678933363106733</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0066350378352099827</v>
       </c>
       <c r="B78">
-        <v>0.00040896886928801191</v>
+        <v>0.00087673903667031573</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.0049762783764074874</v>
       </c>
       <c r="B79">
-        <v>7.7039368524390507E-05</v>
+        <v>0.00048708470674036755</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0033175189176049913</v>
       </c>
       <c r="B80">
-        <v>-0.00022866077622610151</v>
+        <v>0.00010972615336960738</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.0016587594588024957</v>
       </c>
       <c r="B81">
-        <v>-0.00047284943056034482</v>
+        <v>-0.00022735303065757556</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.0019254607130190513</v>
       </c>
       <c r="B2">
-        <v>0.0008823605480244817</v>
+        <v>0.00073987645526107189</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0038509214260381026</v>
       </c>
       <c r="B3">
-        <v>0.0013940254035913501</v>
+        <v>0.0011976284108634065</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0057763821390571539</v>
       </c>
       <c r="B4">
-        <v>0.0018400503255736516</v>
+        <v>0.001602063381444497</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0077018428520762051</v>
       </c>
       <c r="B5">
-        <v>0.0022374383889923223</v>
+        <v>0.001965948428456636</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.0096273035650952556</v>
       </c>
       <c r="B6">
-        <v>0.0025931481429418476</v>
+        <v>0.0022945163460725421</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.011552764278114308</v>
       </c>
       <c r="B7">
-        <v>0.0029111674939359313</v>
+        <v>0.0025907708312895611</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.01347822499113336</v>
       </c>
       <c r="B8">
-        <v>0.0031938567846011121</v>
+        <v>0.00285649435331532</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.01540368570415241</v>
       </c>
       <c r="B9">
-        <v>0.0034448789855272698</v>
+        <v>0.0030944451357578025</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.017329146417171461</v>
       </c>
       <c r="B10">
-        <v>0.0036681839519323331</v>
+        <v>0.0033075959762126385</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.019254607130190511</v>
       </c>
       <c r="B11">
-        <v>0.0038675664495831019</v>
+        <v>0.0034988022138256933</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.021180067843209565</v>
       </c>
       <c r="B12">
-        <v>0.0040450646494489409</v>
+        <v>0.003669601180227724</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.023105528556228615</v>
       </c>
       <c r="B13">
-        <v>0.0041958454327606061</v>
+        <v>0.0038163756354388117</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.025030989269247666</v>
       </c>
       <c r="B14">
-        <v>0.00431702640987186</v>
+        <v>0.0039369708157552226</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.02695644998226672</v>
       </c>
       <c r="B15">
-        <v>0.0044203993973671238</v>
+        <v>0.0040402364341886425</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.028881910695285767</v>
       </c>
       <c r="B16">
-        <v>0.0045167797539499392</v>
+        <v>0.0041342893659042628</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.030807371408304821</v>
       </c>
       <c r="B17">
-        <v>0.0045984028005697005</v>
+        <v>0.00421331065796589</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.032732832121323871</v>
       </c>
       <c r="B18">
-        <v>0.0046552351083122964</v>
+        <v>0.0042697791500095113</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.034658292834342921</v>
       </c>
       <c r="B19">
-        <v>0.0046867482865637546</v>
+        <v>0.0043033006800612438</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.036583753547361972</v>
       </c>
       <c r="B20">
-        <v>0.0046947902042851373</v>
+        <v>0.0043152628357447393</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.038509214260381022</v>
       </c>
       <c r="B21">
-        <v>0.0046812087304375066</v>
+        <v>0.004307053204683645</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.040434674973400073</v>
       </c>
       <c r="B22">
-        <v>0.0046475219116308827</v>
+        <v>0.0042798114564259184</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.04236013568641913</v>
       </c>
       <c r="B23">
-        <v>0.0045939285050711123</v>
+        <v>0.0042336855882167557</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.04428559639943818</v>
       </c>
       <c r="B24">
-        <v>0.0045202974456130026</v>
+        <v>0.0041685756792256591</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.046211057112457231</v>
       </c>
       <c r="B25">
-        <v>0.0044264976681113585</v>
+        <v>0.0040843818086221334</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.048136517825476274</v>
       </c>
       <c r="B26">
-        <v>0.0043123421547504237</v>
+        <v>0.0039809615570644587</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.050061978538495332</v>
       </c>
       <c r="B27">
-        <v>0.004177420077032196</v>
+        <v>0.0038580025111660254</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.051987439251514382</v>
       </c>
       <c r="B28">
-        <v>0.0040212646537881079</v>
+        <v>0.0037151497590290016</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.053912899964533439</v>
       </c>
       <c r="B29">
-        <v>0.0038434091038495972</v>
+        <v>0.003552048388755555</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.05583836067755249</v>
       </c>
       <c r="B30">
-        <v>0.0036436288907013177</v>
+        <v>0.0033685246237909936</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.057763821390571533</v>
       </c>
       <c r="B31">
-        <v>0.0034226684564408042</v>
+        <v>0.0031651292289531915</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.059689282103590584</v>
       </c>
       <c r="B32">
-        <v>0.0031815144878188095</v>
+        <v>0.0029425941044031617</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.061614742816609641</v>
       </c>
       <c r="B33">
-        <v>0.0029211536715860881</v>
+        <v>0.0027016511503019161</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.063540203529628692</v>
       </c>
       <c r="B34">
-        <v>0.0026421759103830429</v>
+        <v>0.0024427340903570762</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.065465664242647742</v>
       </c>
       <c r="B35">
-        <v>0.0023435839704086768</v>
+        <v>0.0021650839424626838</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.067391124955666792</v>
       </c>
       <c r="B36">
-        <v>0.0020239838337516415</v>
+        <v>0.0018676435480593876</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.069316585668685843</v>
       </c>
       <c r="B37">
-        <v>0.0016819814825005863</v>
+        <v>0.0015493557485878342</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.0712420463817049</v>
       </c>
       <c r="B38">
-        <v>0.001315213061660894</v>
+        <v>0.0012084354584756725</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.073167507094723944</v>
       </c>
       <c r="B39">
-        <v>0.00091743536790487266</v>
+        <v>0.00084018588409854841</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.075092967807743</v>
       </c>
       <c r="B40">
-        <v>0.00048143536082156094</v>
+        <v>0.00043918230481910831</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.077018428520762044</v>
       </c>
       <c r="B42">
-        <v>-3.34014190094519E-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.075092967807743</v>
       </c>
       <c r="B43">
-        <v>0.00014341091280194033</v>
+        <v>0.00018566396880439294</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.073167507094723944</v>
       </c>
       <c r="B44">
-        <v>0.00029943949745427919</v>
+        <v>0.00037668898126060334</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.0712420463817049</v>
       </c>
       <c r="B45">
-        <v>0.00046099223617912039</v>
+        <v>0.00056776983936434211</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.069316585668685843</v>
       </c>
       <c r="B46">
-        <v>0.00062097561119856849</v>
+        <v>0.00075360134511132072</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.067391124955666792</v>
       </c>
       <c r="B47">
-        <v>0.00077326154821360594</v>
+        <v>0.00092960183390586033</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.065465664242647742</v>
       </c>
       <c r="B48">
-        <v>0.00091558374684072694</v>
+        <v>0.0010940837747867207</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.063540203529628692</v>
       </c>
       <c r="B49">
-        <v>0.0010466413501753053</v>
+        <v>0.0012460831702012726</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.061614742816609641</v>
       </c>
       <c r="B50">
-        <v>0.0011651335013127132</v>
+        <v>0.0013846360225968849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.059689282103590584</v>
       </c>
       <c r="B51">
-        <v>0.0012701514204936225</v>
+        <v>0.0015090718039092708</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.057763821390571533</v>
       </c>
       <c r="B52">
-        <v>0.0013623546365399031</v>
+        <v>0.0016198938640275158</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.05583836067755249</v>
       </c>
       <c r="B53">
-        <v>0.0014427947554187242</v>
+        <v>0.0017178990223290487</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.053912899964533439</v>
       </c>
       <c r="B54">
-        <v>0.0015125233830972555</v>
+        <v>0.0018038840981912986</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.051987439251514382</v>
       </c>
       <c r="B55">
-        <v>0.001572345495715255</v>
+        <v>0.0018784603904743618</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.050061978538495332</v>
       </c>
       <c r="B56">
-        <v>0.0016220795501028366</v>
+        <v>0.0019414971159690067</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.048136517825476274</v>
       </c>
       <c r="B57">
-        <v>0.0016612973732627037</v>
+        <v>0.0019926779709486687</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.046211057112457231</v>
       </c>
       <c r="B58">
-        <v>0.0016895707921975591</v>
+        <v>0.002031686651686784</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.04428559639943818</v>
       </c>
       <c r="B59">
-        <v>0.0017065233145142572</v>
+        <v>0.0020582450809016007</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.04236013568641913</v>
       </c>
       <c r="B60">
-        <v>0.0017119851702362581</v>
+        <v>0.0020722280870906153</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.040434674973400073</v>
       </c>
       <c r="B61">
-        <v>0.0017058382699911725</v>
+        <v>0.0020735487251961359</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.038509214260381022</v>
       </c>
       <c r="B62">
-        <v>0.0016879645244066109</v>
+        <v>0.0020621200501604732</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.036583753547361972</v>
       </c>
       <c r="B63">
-        <v>0.0016585712559619567</v>
+        <v>0.0020380986245023542</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.034658292834342921</v>
       </c>
       <c r="B64">
-        <v>0.0016191674345436792</v>
+        <v>0.0020026150410461887</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.032732832121323871</v>
       </c>
       <c r="B65">
-        <v>0.0015715874418900191</v>
+        <v>0.0019570434001928037</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.030807371408304821</v>
       </c>
       <c r="B66">
-        <v>0.001517665659739218</v>
+        <v>0.0019027578023430283</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.028881910695285767</v>
       </c>
       <c r="B67">
-        <v>0.0014568566495845312</v>
+        <v>0.0018393470376302072</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.02695644998226672</v>
       </c>
       <c r="B68">
-        <v>0.0013790956919392723</v>
+        <v>0.0017592586551177535</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.025030989269247666</v>
       </c>
       <c r="B69">
-        <v>0.0012765816569387555</v>
+        <v>0.0016566372510553934</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.023105528556228615</v>
       </c>
       <c r="B70">
-        <v>0.001160087054186249</v>
+        <v>0.0015395568515080436</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.021180067843209565</v>
       </c>
       <c r="B71">
-        <v>0.0010413568956792012</v>
+        <v>0.0014168203649004188</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.019254607130190511</v>
       </c>
       <c r="B72">
-        <v>0.00091745256352383255</v>
+        <v>0.0012862167992812412</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.017329146417171461</v>
       </c>
       <c r="B73">
-        <v>0.00078348014617477489</v>
+        <v>0.0011440681218944696</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.01540368570415241</v>
       </c>
       <c r="B74">
-        <v>0.00064140818737153126</v>
+        <v>0.00099184203714099855</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.01347822499113336</v>
       </c>
       <c r="B75">
-        <v>0.000494957334314773</v>
+        <v>0.00083231976560056535</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.011552764278114308</v>
       </c>
       <c r="B76">
-        <v>0.00034799419276497013</v>
+        <v>0.00066839085541134011</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.0096273035650952556</v>
       </c>
       <c r="B77">
-        <v>0.00020409376798740785</v>
+        <v>0.00050272556485671271</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0077018428520762051</v>
       </c>
       <c r="B78">
-        <v>6.5518704706832756E-05</v>
+        <v>0.00033700866524251897</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0057763821390571539</v>
       </c>
       <c r="B79">
-        <v>-6.384522745958621E-05</v>
+        <v>0.00017414171666956861</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0038509214260381026</v>
       </c>
       <c r="B80">
-        <v>-0.0001771505382321956</v>
+        <v>1.92464544957477E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.0019254607130190513</v>
       </c>
       <c r="B81">
-        <v>-0.0002575121940827966</v>
+        <v>-0.00011502810131938676</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0021563872964432446</v>
       </c>
       <c r="B2">
-        <v>0.00065685684997995408</v>
+        <v>0.000497284190043154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0043127745928864892</v>
       </c>
       <c r="B3">
-        <v>0.0010069393261826504</v>
+        <v>0.00078698782194543983</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.0064691618893297342</v>
       </c>
       <c r="B4">
-        <v>0.0013064353855494087</v>
+        <v>0.0010399059157090236</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0086255491857729783</v>
       </c>
       <c r="B5">
-        <v>0.001569585822025602</v>
+        <v>0.0012655352132271047</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.010781936482216223</v>
       </c>
       <c r="B6">
-        <v>0.001802196986561839</v>
+        <v>0.0014677493352912643</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.012938323778659468</v>
       </c>
       <c r="B7">
-        <v>0.0020075831678039026</v>
+        <v>0.001648760321675747</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.015094711075102713</v>
       </c>
       <c r="B8">
-        <v>0.0021876931352682416</v>
+        <v>0.001809869762294185</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.017251098371545957</v>
       </c>
       <c r="B9">
-        <v>0.0023455732001480562</v>
+        <v>0.0019531107121953854</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0194074856679892</v>
       </c>
       <c r="B10">
-        <v>0.0024845122861359586</v>
+        <v>0.00208067785584372</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B11">
-        <v>0.0026076722252454569</v>
+        <v>0.0021946809302306469</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.023720260260875693</v>
       </c>
       <c r="B12">
-        <v>0.0027167409576588286</v>
+        <v>0.0022962469689564312</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.025876647557318937</v>
       </c>
       <c r="B13">
-        <v>0.0028076379479125258</v>
+        <v>0.0023826571395294915</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.028033034853762181</v>
       </c>
       <c r="B14">
-        <v>0.0028779227552135694</v>
+        <v>0.0024522858935762891</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.030189422150205425</v>
       </c>
       <c r="B15">
-        <v>0.0029374837930970709</v>
+        <v>0.0025117266852873166</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.032345809446648666</v>
       </c>
       <c r="B16">
-        <v>0.0029953906658424681</v>
+        <v>0.0025670269977517853</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.034502196743091913</v>
       </c>
       <c r="B17">
-        <v>0.0030451088863784038</v>
+        <v>0.0026138314270897547</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.036658584039535161</v>
       </c>
       <c r="B18">
-        <v>0.0030782001094763643</v>
+        <v>0.0026465152009231266</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.0388149713359784</v>
       </c>
       <c r="B19">
-        <v>0.0030942146486300144</v>
+        <v>0.0026647789598503195</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.040971358632421649</v>
       </c>
       <c r="B20">
-        <v>0.0030946999820135618</v>
+        <v>0.0026696546977138819</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B21">
-        <v>0.0030812035878012138</v>
+        <v>0.0026621744083563628</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.045284133225308137</v>
       </c>
       <c r="B22">
-        <v>0.0030549974268942338</v>
+        <v>0.0026431862956610925</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.047440520521751385</v>
       </c>
       <c r="B23">
-        <v>0.0030162513911021062</v>
+        <v>0.0026128034036745338</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.049596907818194626</v>
       </c>
       <c r="B24">
-        <v>0.0029648598549613693</v>
+        <v>0.0025709549864839304</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.051753295114637873</v>
       </c>
       <c r="B25">
-        <v>0.0029007171930085633</v>
+        <v>0.002517570298176528</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.053909682411081114</v>
       </c>
       <c r="B26">
-        <v>0.002823672253562249</v>
+        <v>0.0024525481343807463</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.056066069707524362</v>
       </c>
       <c r="B27">
-        <v>0.0027333917800690713</v>
+        <v>0.0023756654568897026</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.0582224570039676</v>
       </c>
       <c r="B28">
-        <v>0.0026294969897576984</v>
+        <v>0.0022866687690376911</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.06037884430041085</v>
       </c>
       <c r="B29">
-        <v>0.0025116090998567966</v>
+        <v>0.002185304574159005</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.0625352315968541</v>
       </c>
       <c r="B30">
-        <v>0.0023795543167003828</v>
+        <v>0.0020714559263506835</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B31">
-        <v>0.0022339788030438746</v>
+        <v>0.0019455520827607483</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.066848006189740586</v>
       </c>
       <c r="B32">
-        <v>0.0020757337107480361</v>
+        <v>0.0018081588512999661</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.069004393486183827</v>
       </c>
       <c r="B33">
-        <v>0.0019056701916736342</v>
+        <v>0.0016598420398791041</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.071160780782627067</v>
       </c>
       <c r="B34">
-        <v>0.0017243077567714569</v>
+        <v>0.0015009462494835848</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.073317168079070322</v>
       </c>
       <c r="B35">
-        <v>0.0015308393533523821</v>
+        <v>0.0013309312533974511</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.075473555375513562</v>
       </c>
       <c r="B36">
-        <v>0.0013241262878173111</v>
+        <v>0.001149035617979401</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.0776299426719568</v>
       </c>
       <c r="B37">
-        <v>0.001103029866567142</v>
+        <v>0.00095449790958813106</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.079786329968400044</v>
       </c>
       <c r="B38">
-        <v>0.00086559832174600254</v>
+        <v>0.000746014543434452</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.0819427172648433</v>
       </c>
       <c r="B39">
-        <v>0.00060662758847092563</v>
+        <v>0.00052011333013762286</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.084099104561286539</v>
       </c>
       <c r="B40">
-        <v>0.000320100527602171</v>
+        <v>0.00027277992916901464</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.084099104561286539</v>
       </c>
       <c r="B43">
-        <v>3.6176937003232085E-05</v>
+        <v>8.349753543638859E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.0819427172648433</v>
       </c>
       <c r="B44">
-        <v>8.7542038471108755E-05</v>
+        <v>0.00017405629680441158</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.079786329968400044</v>
       </c>
       <c r="B45">
-        <v>0.00014809565187670049</v>
+        <v>0.00026767943018825074</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.0776299426719568</v>
       </c>
       <c r="B46">
-        <v>0.0002118381246930778</v>
+        <v>0.00036037008167208847</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.075473555375513562</v>
       </c>
       <c r="B47">
-        <v>0.00027358226878985195</v>
+        <v>0.00044867293862776178</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.073317168079070322</v>
       </c>
       <c r="B48">
-        <v>0.00033139075362279637</v>
+        <v>0.00053129885357772731</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.071160780782627067</v>
       </c>
       <c r="B49">
-        <v>0.00038413871304422595</v>
+        <v>0.0006075002203320978</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.069004393486183827</v>
       </c>
       <c r="B50">
-        <v>0.00043070128090645475</v>
+        <v>0.00067652943270098457</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.066848006189740586</v>
       </c>
       <c r="B51">
-        <v>0.00047028455405961575</v>
+        <v>0.00073785941350768577</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.064691618893297331</v>
       </c>
       <c r="B52">
-        <v>0.00050341848134511692</v>
+        <v>0.00079184520162824319</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.0625352315968541</v>
       </c>
       <c r="B53">
-        <v>0.00053096397460218494</v>
+        <v>0.0008390623649518847</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.06037884430041085</v>
       </c>
       <c r="B54">
-        <v>0.00055378194567004655</v>
+        <v>0.00088008647136783829</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.0582224570039676</v>
       </c>
       <c r="B55">
-        <v>0.0005725276654376532</v>
+        <v>0.00091535588615766078</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.056066069707524362</v>
       </c>
       <c r="B56">
-        <v>0.00058703384099285558</v>
+        <v>0.000944760164172225</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.053909682411081114</v>
       </c>
       <c r="B57">
-        <v>0.00059692753847322936</v>
+        <v>0.00096805165765473269</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.051753295114637873</v>
       </c>
       <c r="B58">
-        <v>0.00060183582401635</v>
+        <v>0.00098498271884838568</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.049596907818194626</v>
       </c>
       <c r="B59">
-        <v>0.00060143064409673506</v>
+        <v>0.00099533551257417426</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.047440520521751385</v>
       </c>
       <c r="B60">
-        <v>0.00059556346653667075</v>
+        <v>0.00099901145396424332</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.045284133225308137</v>
       </c>
       <c r="B61">
-        <v>0.00058413063949538523</v>
+        <v>0.00099594177072852676</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.04312774592886489</v>
       </c>
       <c r="B62">
-        <v>0.00056702851113210671</v>
+        <v>0.00098605769057695785</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.040971358632421649</v>
       </c>
       <c r="B63">
-        <v>0.00054442827621548333</v>
+        <v>0.00096947356051516292</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.0388149713359784</v>
       </c>
       <c r="B64">
-        <v>0.00051760051595184365</v>
+        <v>0.00094703620473153875</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.036658584039535161</v>
       </c>
       <c r="B65">
-        <v>0.00048809065815693639</v>
+        <v>0.00091977556671017429</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.034502196743091913</v>
       </c>
       <c r="B66">
-        <v>0.00045744413064651026</v>
+        <v>0.00088872158993515908</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.032345809446648666</v>
       </c>
       <c r="B67">
-        <v>0.00042520865729837014</v>
+        <v>0.00085357232538905308</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.030189422150205425</v>
       </c>
       <c r="B68">
-        <v>0.00038294114623854577</v>
+        <v>0.00080869825404829992</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.028033034853762181</v>
       </c>
       <c r="B69">
-        <v>0.0003241015853898891</v>
+        <v>0.000749738447027169</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.025876647557318937</v>
       </c>
       <c r="B70">
-        <v>0.00025775309761431826</v>
+        <v>0.00068273390599735281</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.023720260260875693</v>
       </c>
       <c r="B71">
-        <v>0.00019377702544444536</v>
+        <v>0.00061427101414684244</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.021563872964432445</v>
       </c>
       <c r="B72">
-        <v>0.00012972445515659601</v>
+        <v>0.00054271575017140615</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0194074856679892</v>
       </c>
       <c r="B73">
-        <v>6.15057043825303E-05</v>
+        <v>0.00046534013467476831</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.017251098371545957</v>
       </c>
       <c r="B74">
-        <v>-9.20172756796718E-06</v>
+        <v>0.00038326076038470335</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.015094711075102713</v>
       </c>
       <c r="B75">
-        <v>-7.9247102576097947E-05</v>
+        <v>0.00029857627039795863</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.012938323778659468</v>
       </c>
       <c r="B76">
-        <v>-0.00014535390896503275</v>
+        <v>0.00021346893716312322</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.010781936482216223</v>
       </c>
       <c r="B77">
-        <v>-0.0002044889210616117</v>
+        <v>0.00012995873020896345</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0086255491857729783</v>
       </c>
       <c r="B78">
-        <v>-0.00025471783076538238</v>
+        <v>4.9332778033114959E-05</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.0064691618893297342</v>
       </c>
       <c r="B79">
-        <v>-0.00029274143349290141</v>
+        <v>-2.6211963652516467E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0043127745928864892</v>
       </c>
       <c r="B80">
-        <v>-0.0003127696992406147</v>
+        <v>-9.2818195003403919E-05</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0021563872964432446</v>
       </c>
       <c r="B81">
-        <v>-0.00030057910964084635</v>
+        <v>-0.00014100644970404633</v>
       </c>
     </row>
     <row r="82" spans="1:2">
